--- a/excel-files/NAVOTAS/NORTH BAY BOULEVARD ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/NORTH BAY BOULEVARD ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A357579D-F72D-41FD-A1FA-7525EC550305}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA74FAB8-ED64-47C9-9A0B-FDC03A12D24B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Math</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Science</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -742,6 +742,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -753,12 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3711,17 +3711,25 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>133</v>
+      </c>
+      <c r="D11" s="1">
+        <v>161</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3814,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3884,7 +3892,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3904,7 +3912,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>150</v>
@@ -3916,7 +3924,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
@@ -3944,7 +3952,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -3972,7 +3980,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -4000,7 +4008,7 @@
         <v>2024</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
@@ -4016,7 +4024,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>150</v>
@@ -4028,7 +4036,7 @@
         <v>2024</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
@@ -4056,7 +4064,7 @@
         <v>2024</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
@@ -4094,17 +4102,25 @@
       <c r="B29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>150</v>
+      </c>
+      <c r="D29" s="1">
+        <v>266</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4122,19 +4138,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="C31" s="1">
+        <v>130</v>
+      </c>
+      <c r="D31" s="1">
+        <v>162</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4142,7 +4166,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4204,17 +4228,25 @@
       <c r="B35" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+      <c r="C35" s="1">
+        <v>130</v>
+      </c>
+      <c r="D35" s="1">
+        <v>170</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1">
@@ -4222,19 +4254,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
+        <v>130</v>
+      </c>
+      <c r="D36" s="1">
+        <v>162</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4244,17 +4284,25 @@
       <c r="B37" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+      <c r="C37" s="1">
+        <v>130</v>
+      </c>
+      <c r="D37" s="1">
+        <v>162</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4264,17 +4312,25 @@
       <c r="B38" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>130</v>
+      </c>
+      <c r="D38" s="1">
+        <v>162</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4312,7 +4368,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4332,7 +4388,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4412,7 +4468,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4502,7 +4558,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4522,7 +4578,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4602,7 +4658,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4692,7 +4748,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4712,7 +4768,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4792,7 +4848,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4882,7 +4938,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4902,7 +4958,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -4982,7 +5038,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5072,7 +5128,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5092,7 +5148,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5172,7 +5228,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5424,10 +5480,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21:E29 E14:E19 E8:E12 E2:E6 E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F2:F6 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F91:F98 F8:F12 F21:F29" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F2:F6 F21:F29 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F91:F98 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5440,7 +5496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5470,38 +5526,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5540,10 +5596,10 @@
       <c r="L2" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5576,10 +5632,10 @@
       <c r="X2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>60</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -6015,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6084,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6588,7 +6644,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1">
         <v>131</v>
@@ -6671,7 +6727,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="5">
@@ -7030,7 +7086,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -7237,7 +7293,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -7306,7 +7362,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="5">
@@ -7458,7 +7514,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7527,7 +7583,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7803,7 +7859,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -8088,24 +8144,33 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C43" s="1">
+        <v>130</v>
+      </c>
       <c r="D43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="5"/>
+        <v>1040</v>
+      </c>
+      <c r="E43" s="5">
+        <f>58*8</f>
+        <v>464</v>
+      </c>
+      <c r="F43" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
@@ -8113,29 +8178,36 @@
       </c>
       <c r="J43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="5"/>
+        <v>1040</v>
+      </c>
+      <c r="K43" s="5">
+        <f>312*8</f>
+        <v>2496</v>
+      </c>
+      <c r="L43" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1456</v>
       </c>
       <c r="P43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="13"/>
@@ -8143,38 +8215,47 @@
       </c>
       <c r="V43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="C44" s="1">
+        <v>130</v>
+      </c>
       <c r="D44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="5"/>
+        <v>1040</v>
+      </c>
+      <c r="E44" s="5">
+        <f t="shared" ref="E44:E46" si="16">58*8</f>
+        <v>464</v>
+      </c>
+      <c r="F44" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="H44" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="3"/>
@@ -8182,29 +8263,36 @@
       </c>
       <c r="J44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K44" s="5"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="5"/>
+        <v>1040</v>
+      </c>
+      <c r="K44" s="5">
+        <f>387*8</f>
+        <v>3096</v>
+      </c>
+      <c r="L44" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N44" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O44" s="5">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2056</v>
       </c>
       <c r="P44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" si="13"/>
@@ -8212,38 +8300,47 @@
       </c>
       <c r="V44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W44" s="5"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1">
+        <v>130</v>
+      </c>
       <c r="D45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="5"/>
+        <v>1040</v>
+      </c>
+      <c r="E45" s="5">
+        <f t="shared" si="16"/>
+        <v>464</v>
+      </c>
+      <c r="F45" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
@@ -8251,14 +8348,14 @@
       </c>
       <c r="J45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="11"/>
@@ -8266,14 +8363,14 @@
       </c>
       <c r="P45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="13"/>
@@ -8281,38 +8378,47 @@
       </c>
       <c r="V45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1">
+        <v>130</v>
+      </c>
       <c r="D46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="5"/>
+        <v>1040</v>
+      </c>
+      <c r="E46" s="5">
+        <f t="shared" si="16"/>
+        <v>464</v>
+      </c>
+      <c r="F46" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="H46" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -8320,14 +8426,14 @@
       </c>
       <c r="J46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O46" s="5">
         <f t="shared" si="11"/>
@@ -8335,14 +8441,14 @@
       </c>
       <c r="P46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" si="13"/>
@@ -8350,21 +8456,21 @@
       </c>
       <c r="V46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W46" s="5"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8433,24 +8539,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="C48" s="1">
+        <v>130</v>
+      </c>
       <c r="D48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="5"/>
+        <v>1040</v>
+      </c>
+      <c r="E48" s="5">
+        <f>58*8</f>
+        <v>464</v>
+      </c>
+      <c r="F48" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="H48" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="3"/>
@@ -8458,14 +8573,14 @@
       </c>
       <c r="J48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O48" s="5">
         <f t="shared" si="11"/>
@@ -8473,14 +8588,14 @@
       </c>
       <c r="P48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" si="13"/>
@@ -8488,14 +8603,14 @@
       </c>
       <c r="V48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W48" s="5"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA48" s="5">
         <f t="shared" si="15"/>
@@ -8571,24 +8686,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="1"/>
+      <c r="C50" s="1">
+        <v>130</v>
+      </c>
       <c r="D50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="5"/>
+        <v>1040</v>
+      </c>
+      <c r="E50" s="5">
+        <f>58*8</f>
+        <v>464</v>
+      </c>
+      <c r="F50" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="H50" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" si="3"/>
@@ -8596,14 +8720,14 @@
       </c>
       <c r="J50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O50" s="5">
         <f t="shared" si="11"/>
@@ -8611,14 +8735,14 @@
       </c>
       <c r="P50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U50" s="5">
         <f t="shared" si="13"/>
@@ -8626,14 +8750,14 @@
       </c>
       <c r="V50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W50" s="5"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA50" s="5">
         <f t="shared" si="15"/>
@@ -8728,7 +8852,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8797,7 +8921,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -9073,7 +9197,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9363,7 +9487,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9432,7 +9556,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9708,7 +9832,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -9872,11 +9996,11 @@
       <c r="L70" s="10"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
-        <f t="shared" ref="N70:N126" si="16">IF((J70-K70)&lt;0,0,(J70-K70))</f>
+        <f t="shared" ref="N70:N126" si="17">IF((J70-K70)&lt;0,0,(J70-K70))</f>
         <v>0</v>
       </c>
       <c r="O70" s="12">
-        <f t="shared" ref="O70:O126" si="17">IF((K70-J70)&lt;0,0,(K70-J70))</f>
+        <f t="shared" ref="O70:O126" si="18">IF((K70-J70)&lt;0,0,(K70-J70))</f>
         <v>0</v>
       </c>
       <c r="P70" s="12">
@@ -9887,11 +10011,11 @@
       <c r="R70" s="10"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12">
-        <f t="shared" ref="T70:T127" si="18">IF((P70-Q70)&lt;0,0,(P70-Q70))</f>
+        <f t="shared" ref="T70:T127" si="19">IF((P70-Q70)&lt;0,0,(P70-Q70))</f>
         <v>0</v>
       </c>
       <c r="U70" s="12">
-        <f t="shared" ref="U70:U127" si="19">IF((Q70-P70)&lt;0,0,(Q70-P70))</f>
+        <f t="shared" ref="U70:U127" si="20">IF((Q70-P70)&lt;0,0,(Q70-P70))</f>
         <v>0</v>
       </c>
       <c r="V70" s="12">
@@ -9902,11 +10026,11 @@
       <c r="X70" s="10"/>
       <c r="Y70" s="12"/>
       <c r="Z70" s="12">
-        <f t="shared" ref="Z70:Z127" si="20">IF((V70-W70)&lt;0,0,(V70-W70))</f>
+        <f t="shared" ref="Z70:Z127" si="21">IF((V70-W70)&lt;0,0,(V70-W70))</f>
         <v>0</v>
       </c>
       <c r="AA70" s="12">
-        <f t="shared" ref="AA70:AA127" si="21">IF((W70-V70)&lt;0,0,(W70-V70))</f>
+        <f t="shared" ref="AA70:AA127" si="22">IF((W70-V70)&lt;0,0,(W70-V70))</f>
         <v>0</v>
       </c>
     </row>
@@ -9941,11 +10065,11 @@
       <c r="L71" s="10"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O71" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P71" s="12">
@@ -9956,11 +10080,11 @@
       <c r="R71" s="10"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U71" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V71" s="12">
@@ -9971,11 +10095,11 @@
       <c r="X71" s="10"/>
       <c r="Y71" s="12"/>
       <c r="Z71" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA71" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -9998,7 +10122,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10024,11 +10148,11 @@
       <c r="L73" s="10"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O73" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P73" s="12">
@@ -10039,11 +10163,11 @@
       <c r="R73" s="10"/>
       <c r="S73" s="12"/>
       <c r="T73" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U73" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V73" s="12">
@@ -10054,11 +10178,11 @@
       <c r="X73" s="10"/>
       <c r="Y73" s="12"/>
       <c r="Z73" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA73" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10067,7 +10191,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10093,11 +10217,11 @@
       <c r="L74" s="10"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O74" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P74" s="12">
@@ -10108,11 +10232,11 @@
       <c r="R74" s="10"/>
       <c r="S74" s="12"/>
       <c r="T74" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U74" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V74" s="12">
@@ -10123,11 +10247,11 @@
       <c r="X74" s="10"/>
       <c r="Y74" s="12"/>
       <c r="Z74" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA74" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10162,11 +10286,11 @@
       <c r="L75" s="10"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O75" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P75" s="12">
@@ -10177,11 +10301,11 @@
       <c r="R75" s="10"/>
       <c r="S75" s="12"/>
       <c r="T75" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U75" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V75" s="12">
@@ -10192,11 +10316,11 @@
       <c r="X75" s="10"/>
       <c r="Y75" s="12"/>
       <c r="Z75" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA75" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10231,11 +10355,11 @@
       <c r="L76" s="10"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O76" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P76" s="12">
@@ -10246,11 +10370,11 @@
       <c r="R76" s="10"/>
       <c r="S76" s="12"/>
       <c r="T76" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U76" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V76" s="12">
@@ -10261,11 +10385,11 @@
       <c r="X76" s="10"/>
       <c r="Y76" s="12"/>
       <c r="Z76" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA76" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10300,11 +10424,11 @@
       <c r="L77" s="10"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O77" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P77" s="12">
@@ -10315,11 +10439,11 @@
       <c r="R77" s="10"/>
       <c r="S77" s="12"/>
       <c r="T77" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U77" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V77" s="12">
@@ -10330,11 +10454,11 @@
       <c r="X77" s="10"/>
       <c r="Y77" s="12"/>
       <c r="Z77" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA77" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10343,7 +10467,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10354,11 +10478,11 @@
       <c r="F78" s="10"/>
       <c r="G78" s="12"/>
       <c r="H78" s="12">
-        <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
+        <f t="shared" ref="H78:H127" si="23">IF((D78-E78)&lt;0,0,(D78-E78))</f>
         <v>0</v>
       </c>
       <c r="I78" s="12">
-        <f t="shared" ref="I78:I127" si="23">IF((E78-D78)&lt;0,0,(E78-D78))</f>
+        <f t="shared" ref="I78:I127" si="24">IF((E78-D78)&lt;0,0,(E78-D78))</f>
         <v>0</v>
       </c>
       <c r="J78" s="12">
@@ -10369,11 +10493,11 @@
       <c r="L78" s="10"/>
       <c r="M78" s="12"/>
       <c r="N78" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O78" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P78" s="12">
@@ -10384,11 +10508,11 @@
       <c r="R78" s="10"/>
       <c r="S78" s="12"/>
       <c r="T78" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U78" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V78" s="12">
@@ -10399,11 +10523,11 @@
       <c r="X78" s="10"/>
       <c r="Y78" s="12"/>
       <c r="Z78" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA78" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10423,11 +10547,11 @@
       <c r="F79" s="10"/>
       <c r="G79" s="12"/>
       <c r="H79" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I79" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J79" s="12">
@@ -10438,11 +10562,11 @@
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O79" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P79" s="12">
@@ -10453,11 +10577,11 @@
       <c r="R79" s="10"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U79" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V79" s="12">
@@ -10468,11 +10592,11 @@
       <c r="X79" s="10"/>
       <c r="Y79" s="12"/>
       <c r="Z79" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA79" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10492,11 +10616,11 @@
       <c r="F80" s="10"/>
       <c r="G80" s="12"/>
       <c r="H80" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I80" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J80" s="12">
@@ -10507,11 +10631,11 @@
       <c r="L80" s="10"/>
       <c r="M80" s="12"/>
       <c r="N80" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O80" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P80" s="12">
@@ -10522,11 +10646,11 @@
       <c r="R80" s="10"/>
       <c r="S80" s="12"/>
       <c r="T80" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U80" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V80" s="12">
@@ -10537,11 +10661,11 @@
       <c r="X80" s="10"/>
       <c r="Y80" s="12"/>
       <c r="Z80" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA80" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10561,11 +10685,11 @@
       <c r="F81" s="10"/>
       <c r="G81" s="12"/>
       <c r="H81" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I81" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J81" s="12">
@@ -10576,11 +10700,11 @@
       <c r="L81" s="10"/>
       <c r="M81" s="12"/>
       <c r="N81" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O81" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P81" s="12">
@@ -10591,11 +10715,11 @@
       <c r="R81" s="10"/>
       <c r="S81" s="12"/>
       <c r="T81" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U81" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V81" s="12">
@@ -10606,11 +10730,11 @@
       <c r="X81" s="10"/>
       <c r="Y81" s="12"/>
       <c r="Z81" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA81" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10633,7 +10757,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10644,11 +10768,11 @@
       <c r="F83" s="10"/>
       <c r="G83" s="12"/>
       <c r="H83" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I83" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J83" s="12">
@@ -10659,11 +10783,11 @@
       <c r="L83" s="10"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O83" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P83" s="12">
@@ -10674,11 +10798,11 @@
       <c r="R83" s="10"/>
       <c r="S83" s="12"/>
       <c r="T83" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U83" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V83" s="12">
@@ -10689,11 +10813,11 @@
       <c r="X83" s="10"/>
       <c r="Y83" s="12"/>
       <c r="Z83" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA83" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10702,7 +10826,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -10713,11 +10837,11 @@
       <c r="F84" s="10"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I84" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J84" s="12">
@@ -10728,11 +10852,11 @@
       <c r="L84" s="10"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O84" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P84" s="12">
@@ -10743,11 +10867,11 @@
       <c r="R84" s="10"/>
       <c r="S84" s="12"/>
       <c r="T84" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U84" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V84" s="12">
@@ -10758,11 +10882,11 @@
       <c r="X84" s="10"/>
       <c r="Y84" s="12"/>
       <c r="Z84" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA84" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10782,11 +10906,11 @@
       <c r="F85" s="10"/>
       <c r="G85" s="12"/>
       <c r="H85" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I85" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J85" s="12">
@@ -10797,11 +10921,11 @@
       <c r="L85" s="10"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O85" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P85" s="12">
@@ -10812,11 +10936,11 @@
       <c r="R85" s="10"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U85" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V85" s="12">
@@ -10827,11 +10951,11 @@
       <c r="X85" s="10"/>
       <c r="Y85" s="12"/>
       <c r="Z85" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA85" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10851,11 +10975,11 @@
       <c r="F86" s="10"/>
       <c r="G86" s="12"/>
       <c r="H86" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I86" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J86" s="12">
@@ -10866,11 +10990,11 @@
       <c r="L86" s="10"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O86" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P86" s="12">
@@ -10881,11 +11005,11 @@
       <c r="R86" s="10"/>
       <c r="S86" s="12"/>
       <c r="T86" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U86" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V86" s="12">
@@ -10896,11 +11020,11 @@
       <c r="X86" s="10"/>
       <c r="Y86" s="12"/>
       <c r="Z86" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA86" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10920,11 +11044,11 @@
       <c r="F87" s="10"/>
       <c r="G87" s="12"/>
       <c r="H87" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I87" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J87" s="12">
@@ -10935,11 +11059,11 @@
       <c r="L87" s="10"/>
       <c r="M87" s="12"/>
       <c r="N87" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O87" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P87" s="12">
@@ -10950,11 +11074,11 @@
       <c r="R87" s="10"/>
       <c r="S87" s="12"/>
       <c r="T87" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U87" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V87" s="12">
@@ -10965,11 +11089,11 @@
       <c r="X87" s="10"/>
       <c r="Y87" s="12"/>
       <c r="Z87" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA87" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10978,7 +11102,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -10989,11 +11113,11 @@
       <c r="F88" s="10"/>
       <c r="G88" s="12"/>
       <c r="H88" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I88" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J88" s="12">
@@ -11004,11 +11128,11 @@
       <c r="L88" s="10"/>
       <c r="M88" s="12"/>
       <c r="N88" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O88" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P88" s="12">
@@ -11019,11 +11143,11 @@
       <c r="R88" s="10"/>
       <c r="S88" s="12"/>
       <c r="T88" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U88" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V88" s="12">
@@ -11034,11 +11158,11 @@
       <c r="X88" s="10"/>
       <c r="Y88" s="12"/>
       <c r="Z88" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA88" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11058,11 +11182,11 @@
       <c r="F89" s="10"/>
       <c r="G89" s="12"/>
       <c r="H89" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I89" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J89" s="12">
@@ -11073,11 +11197,11 @@
       <c r="L89" s="10"/>
       <c r="M89" s="12"/>
       <c r="N89" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O89" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P89" s="12">
@@ -11088,11 +11212,11 @@
       <c r="R89" s="10"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U89" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V89" s="12">
@@ -11103,11 +11227,11 @@
       <c r="X89" s="10"/>
       <c r="Y89" s="12"/>
       <c r="Z89" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA89" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11127,11 +11251,11 @@
       <c r="F90" s="10"/>
       <c r="G90" s="12"/>
       <c r="H90" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I90" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J90" s="12">
@@ -11142,11 +11266,11 @@
       <c r="L90" s="10"/>
       <c r="M90" s="12"/>
       <c r="N90" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O90" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P90" s="12">
@@ -11157,11 +11281,11 @@
       <c r="R90" s="10"/>
       <c r="S90" s="12"/>
       <c r="T90" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U90" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V90" s="12">
@@ -11172,11 +11296,11 @@
       <c r="X90" s="10"/>
       <c r="Y90" s="12"/>
       <c r="Z90" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA90" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11196,11 +11320,11 @@
       <c r="F91" s="10"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I91" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J91" s="12">
@@ -11211,11 +11335,11 @@
       <c r="L91" s="10"/>
       <c r="M91" s="12"/>
       <c r="N91" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O91" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P91" s="12">
@@ -11226,11 +11350,11 @@
       <c r="R91" s="10"/>
       <c r="S91" s="12"/>
       <c r="T91" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U91" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V91" s="12">
@@ -11241,11 +11365,11 @@
       <c r="X91" s="10"/>
       <c r="Y91" s="12"/>
       <c r="Z91" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA91" s="12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11268,7 +11392,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11337,7 +11461,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11613,7 +11737,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -11914,11 +12038,11 @@
       <c r="F103" s="1"/>
       <c r="G103" s="5"/>
       <c r="H103" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I103" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J103" s="5">
@@ -11929,11 +12053,11 @@
       <c r="L103" s="1"/>
       <c r="M103" s="5"/>
       <c r="N103" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O103" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P103" s="5">
@@ -11944,11 +12068,11 @@
       <c r="R103" s="1"/>
       <c r="S103" s="5"/>
       <c r="T103" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U103" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V103" s="5">
@@ -11959,11 +12083,11 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="5"/>
       <c r="Z103" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA103" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -11983,11 +12107,11 @@
       <c r="F104" s="1"/>
       <c r="G104" s="5"/>
       <c r="H104" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I104" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J104" s="5">
@@ -11998,11 +12122,11 @@
       <c r="L104" s="1"/>
       <c r="M104" s="5"/>
       <c r="N104" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O104" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P104" s="5">
@@ -12013,11 +12137,11 @@
       <c r="R104" s="1"/>
       <c r="S104" s="5"/>
       <c r="T104" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U104" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V104" s="5">
@@ -12028,11 +12152,11 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="5"/>
       <c r="Z104" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA104" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12052,11 +12176,11 @@
       <c r="F105" s="1"/>
       <c r="G105" s="5"/>
       <c r="H105" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I105" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J105" s="5">
@@ -12067,11 +12191,11 @@
       <c r="L105" s="1"/>
       <c r="M105" s="5"/>
       <c r="N105" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O105" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P105" s="5">
@@ -12082,11 +12206,11 @@
       <c r="R105" s="1"/>
       <c r="S105" s="5"/>
       <c r="T105" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U105" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V105" s="5">
@@ -12097,11 +12221,11 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="5"/>
       <c r="Z105" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA105" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12121,11 +12245,11 @@
       <c r="F106" s="1"/>
       <c r="G106" s="5"/>
       <c r="H106" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I106" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J106" s="5">
@@ -12136,11 +12260,11 @@
       <c r="L106" s="1"/>
       <c r="M106" s="5"/>
       <c r="N106" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O106" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P106" s="5">
@@ -12151,11 +12275,11 @@
       <c r="R106" s="1"/>
       <c r="S106" s="5"/>
       <c r="T106" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U106" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V106" s="5">
@@ -12166,11 +12290,11 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="5"/>
       <c r="Z106" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA106" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12190,11 +12314,11 @@
       <c r="F107" s="1"/>
       <c r="G107" s="5"/>
       <c r="H107" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I107" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J107" s="5">
@@ -12205,11 +12329,11 @@
       <c r="L107" s="1"/>
       <c r="M107" s="5"/>
       <c r="N107" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O107" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P107" s="5">
@@ -12220,11 +12344,11 @@
       <c r="R107" s="1"/>
       <c r="S107" s="5"/>
       <c r="T107" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U107" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V107" s="5">
@@ -12235,11 +12359,11 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="5"/>
       <c r="Z107" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA107" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12259,11 +12383,11 @@
       <c r="F108" s="1"/>
       <c r="G108" s="5"/>
       <c r="H108" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I108" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J108" s="5">
@@ -12274,11 +12398,11 @@
       <c r="L108" s="1"/>
       <c r="M108" s="5"/>
       <c r="N108" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O108" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P108" s="5">
@@ -12289,11 +12413,11 @@
       <c r="R108" s="1"/>
       <c r="S108" s="5"/>
       <c r="T108" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U108" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V108" s="5">
@@ -12304,11 +12428,11 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="5"/>
       <c r="Z108" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA108" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12328,11 +12452,11 @@
       <c r="F109" s="1"/>
       <c r="G109" s="5"/>
       <c r="H109" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I109" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J109" s="5">
@@ -12343,11 +12467,11 @@
       <c r="L109" s="1"/>
       <c r="M109" s="5"/>
       <c r="N109" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O109" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P109" s="5">
@@ -12358,11 +12482,11 @@
       <c r="R109" s="1"/>
       <c r="S109" s="5"/>
       <c r="T109" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U109" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V109" s="5">
@@ -12373,11 +12497,11 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="5"/>
       <c r="Z109" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA109" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12397,11 +12521,11 @@
       <c r="F110" s="1"/>
       <c r="G110" s="5"/>
       <c r="H110" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I110" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J110" s="5">
@@ -12412,11 +12536,11 @@
       <c r="L110" s="1"/>
       <c r="M110" s="5"/>
       <c r="N110" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O110" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P110" s="5">
@@ -12427,11 +12551,11 @@
       <c r="R110" s="1"/>
       <c r="S110" s="5"/>
       <c r="T110" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U110" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V110" s="5">
@@ -12442,11 +12566,11 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="5"/>
       <c r="Z110" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA110" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12470,11 +12594,11 @@
       <c r="F112" s="1"/>
       <c r="G112" s="5"/>
       <c r="H112" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I112" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J112" s="5">
@@ -12485,11 +12609,11 @@
       <c r="L112" s="1"/>
       <c r="M112" s="5"/>
       <c r="N112" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O112" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P112" s="5">
@@ -12500,11 +12624,11 @@
       <c r="R112" s="1"/>
       <c r="S112" s="5"/>
       <c r="T112" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U112" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V112" s="5">
@@ -12515,11 +12639,11 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="5"/>
       <c r="Z112" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA112" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12532,11 +12656,11 @@
       <c r="F113" s="1"/>
       <c r="G113" s="5"/>
       <c r="H113" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I113" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J113" s="5">
@@ -12547,11 +12671,11 @@
       <c r="L113" s="1"/>
       <c r="M113" s="5"/>
       <c r="N113" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O113" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P113" s="5">
@@ -12562,11 +12686,11 @@
       <c r="R113" s="1"/>
       <c r="S113" s="5"/>
       <c r="T113" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U113" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V113" s="5">
@@ -12577,11 +12701,11 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="5"/>
       <c r="Z113" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA113" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12594,11 +12718,11 @@
       <c r="F114" s="1"/>
       <c r="G114" s="5"/>
       <c r="H114" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I114" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J114" s="5">
@@ -12609,11 +12733,11 @@
       <c r="L114" s="1"/>
       <c r="M114" s="5"/>
       <c r="N114" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O114" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P114" s="5">
@@ -12624,11 +12748,11 @@
       <c r="R114" s="1"/>
       <c r="S114" s="5"/>
       <c r="T114" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U114" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V114" s="5">
@@ -12639,11 +12763,11 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="5"/>
       <c r="Z114" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA114" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12656,11 +12780,11 @@
       <c r="F115" s="1"/>
       <c r="G115" s="5"/>
       <c r="H115" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I115" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J115" s="5">
@@ -12671,11 +12795,11 @@
       <c r="L115" s="1"/>
       <c r="M115" s="5"/>
       <c r="N115" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O115" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P115" s="5">
@@ -12686,11 +12810,11 @@
       <c r="R115" s="1"/>
       <c r="S115" s="5"/>
       <c r="T115" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U115" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V115" s="5">
@@ -12701,11 +12825,11 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="5"/>
       <c r="Z115" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA115" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12718,11 +12842,11 @@
       <c r="F116" s="1"/>
       <c r="G116" s="5"/>
       <c r="H116" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I116" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J116" s="5">
@@ -12733,11 +12857,11 @@
       <c r="L116" s="1"/>
       <c r="M116" s="5"/>
       <c r="N116" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O116" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P116" s="5">
@@ -12748,11 +12872,11 @@
       <c r="R116" s="1"/>
       <c r="S116" s="5"/>
       <c r="T116" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U116" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V116" s="5">
@@ -12763,11 +12887,11 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="5"/>
       <c r="Z116" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA116" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12780,11 +12904,11 @@
       <c r="F117" s="1"/>
       <c r="G117" s="5"/>
       <c r="H117" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I117" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J117" s="5">
@@ -12795,11 +12919,11 @@
       <c r="L117" s="1"/>
       <c r="M117" s="5"/>
       <c r="N117" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O117" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P117" s="5">
@@ -12810,11 +12934,11 @@
       <c r="R117" s="1"/>
       <c r="S117" s="5"/>
       <c r="T117" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U117" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V117" s="5">
@@ -12825,11 +12949,11 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="5"/>
       <c r="Z117" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA117" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12842,11 +12966,11 @@
       <c r="F118" s="1"/>
       <c r="G118" s="5"/>
       <c r="H118" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I118" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J118" s="5">
@@ -12857,11 +12981,11 @@
       <c r="L118" s="1"/>
       <c r="M118" s="5"/>
       <c r="N118" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O118" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P118" s="5">
@@ -12872,11 +12996,11 @@
       <c r="R118" s="1"/>
       <c r="S118" s="5"/>
       <c r="T118" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U118" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V118" s="5">
@@ -12887,11 +13011,11 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="5"/>
       <c r="Z118" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA118" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12904,11 +13028,11 @@
       <c r="F119" s="1"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I119" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J119" s="5">
@@ -12919,11 +13043,11 @@
       <c r="L119" s="1"/>
       <c r="M119" s="5"/>
       <c r="N119" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O119" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P119" s="5">
@@ -12934,11 +13058,11 @@
       <c r="R119" s="1"/>
       <c r="S119" s="5"/>
       <c r="T119" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U119" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V119" s="5">
@@ -12949,11 +13073,11 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="5"/>
       <c r="Z119" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA119" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -12966,11 +13090,11 @@
       <c r="F120" s="1"/>
       <c r="G120" s="5"/>
       <c r="H120" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I120" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J120" s="5">
@@ -12981,11 +13105,11 @@
       <c r="L120" s="1"/>
       <c r="M120" s="5"/>
       <c r="N120" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O120" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P120" s="5">
@@ -12996,11 +13120,11 @@
       <c r="R120" s="1"/>
       <c r="S120" s="5"/>
       <c r="T120" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U120" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V120" s="5">
@@ -13011,11 +13135,11 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="5"/>
       <c r="Z120" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA120" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13028,11 +13152,11 @@
       <c r="F121" s="1"/>
       <c r="G121" s="5"/>
       <c r="H121" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I121" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J121" s="5">
@@ -13043,11 +13167,11 @@
       <c r="L121" s="1"/>
       <c r="M121" s="5"/>
       <c r="N121" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O121" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P121" s="5">
@@ -13058,11 +13182,11 @@
       <c r="R121" s="1"/>
       <c r="S121" s="5"/>
       <c r="T121" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U121" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V121" s="5">
@@ -13073,11 +13197,11 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="5"/>
       <c r="Z121" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA121" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13090,11 +13214,11 @@
       <c r="F122" s="1"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I122" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J122" s="5">
@@ -13105,11 +13229,11 @@
       <c r="L122" s="1"/>
       <c r="M122" s="5"/>
       <c r="N122" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O122" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P122" s="5">
@@ -13120,11 +13244,11 @@
       <c r="R122" s="1"/>
       <c r="S122" s="5"/>
       <c r="T122" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U122" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V122" s="5">
@@ -13135,11 +13259,11 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="5"/>
       <c r="Z122" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA122" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13152,11 +13276,11 @@
       <c r="F123" s="1"/>
       <c r="G123" s="5"/>
       <c r="H123" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I123" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J123" s="5">
@@ -13167,11 +13291,11 @@
       <c r="L123" s="1"/>
       <c r="M123" s="5"/>
       <c r="N123" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O123" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P123" s="5">
@@ -13182,11 +13306,11 @@
       <c r="R123" s="1"/>
       <c r="S123" s="5"/>
       <c r="T123" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U123" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V123" s="5">
@@ -13197,11 +13321,11 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="5"/>
       <c r="Z123" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA123" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13214,11 +13338,11 @@
       <c r="F124" s="1"/>
       <c r="G124" s="5"/>
       <c r="H124" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I124" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J124" s="5">
@@ -13229,11 +13353,11 @@
       <c r="L124" s="1"/>
       <c r="M124" s="5"/>
       <c r="N124" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O124" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P124" s="5">
@@ -13244,11 +13368,11 @@
       <c r="R124" s="1"/>
       <c r="S124" s="5"/>
       <c r="T124" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U124" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V124" s="5">
@@ -13259,11 +13383,11 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="5"/>
       <c r="Z124" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA124" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13276,11 +13400,11 @@
       <c r="F125" s="1"/>
       <c r="G125" s="5"/>
       <c r="H125" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I125" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J125" s="5">
@@ -13291,11 +13415,11 @@
       <c r="L125" s="1"/>
       <c r="M125" s="5"/>
       <c r="N125" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O125" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P125" s="5">
@@ -13306,11 +13430,11 @@
       <c r="R125" s="1"/>
       <c r="S125" s="5"/>
       <c r="T125" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U125" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V125" s="5">
@@ -13321,11 +13445,11 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="5"/>
       <c r="Z125" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA125" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13338,11 +13462,11 @@
       <c r="F126" s="1"/>
       <c r="G126" s="5"/>
       <c r="H126" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I126" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J126" s="5">
@@ -13353,11 +13477,11 @@
       <c r="L126" s="1"/>
       <c r="M126" s="5"/>
       <c r="N126" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O126" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P126" s="5">
@@ -13368,11 +13492,11 @@
       <c r="R126" s="1"/>
       <c r="S126" s="5"/>
       <c r="T126" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U126" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V126" s="5">
@@ -13383,11 +13507,11 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="5"/>
       <c r="Z126" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA126" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -13400,11 +13524,11 @@
       <c r="F127" s="29"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I127" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J127" s="5">
@@ -13415,11 +13539,11 @@
       <c r="L127" s="29"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
-        <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
+        <f t="shared" ref="N127" si="25">IF((J127-K127)&lt;0,0,(J127-K127))</f>
         <v>0</v>
       </c>
       <c r="O127" s="5">
-        <f t="shared" ref="O127" si="25">IF((K127-J127)&lt;0,0,(K127-J127))</f>
+        <f t="shared" ref="O127" si="26">IF((K127-J127)&lt;0,0,(K127-J127))</f>
         <v>0</v>
       </c>
       <c r="P127" s="5"/>
@@ -13427,11 +13551,11 @@
       <c r="R127" s="29"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="U127" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V127" s="5">
@@ -13442,199 +13566,25 @@
       <c r="X127" s="29"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AA127" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C51 C49 C47" name="Textbooks"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D43:F51 K43:L51" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 G43:G51" name="SOURCE"/>
+    <protectedRange sqref="C44" name="Textbooks_1"/>
+    <protectedRange sqref="C50" name="Textbooks_2"/>
+    <protectedRange sqref="C48" name="Textbooks_3"/>
+    <protectedRange sqref="C43" name="Textbooks_4"/>
+    <protectedRange sqref="C46" name="Textbooks_5"/>
+    <protectedRange sqref="C45" name="Textbooks_6"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13647,10 +13597,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 X5:X12 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 F43:F51" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G103:G110 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G43:G51" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13666,7 +13616,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13696,38 +13646,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13766,10 +13716,10 @@
       <c r="L2" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -13802,10 +13752,10 @@
       <c r="X2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -14162,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14231,7 +14181,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14715,7 +14665,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -14784,7 +14734,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -14848,7 +14798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15130,7 +15080,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15337,7 +15287,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15406,7 +15356,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15545,7 +15495,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15614,7 +15564,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15890,7 +15840,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -16305,7 +16255,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16374,7 +16324,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16650,7 +16600,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -17065,7 +17015,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
         <v>161</v>
@@ -17160,7 +17110,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
         <v>161</v>
@@ -17516,7 +17466,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1">
         <v>161</v>
@@ -17997,7 +17947,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -18066,7 +18016,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18342,7 +18292,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18757,7 +18707,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18826,7 +18776,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -19102,7 +19052,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19517,7 +19467,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19586,7 +19536,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19862,7 +19812,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -20277,7 +20227,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20346,7 +20296,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20622,7 +20572,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -22095,186 +22045,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101 C55:C65" name="Textbooks"/>
@@ -22292,8 +22062,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 S55:S65 M55:M65 M115:M122 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 Y55:Y65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 R55:R65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 F55:F65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 L55:L65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F103:F113 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
